--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-17 10:15</t>
+          <t>更新时间: 2026-08-18 08:22</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-18 08:22</t>
+          <t>更新时间: 2026-08-18 08:30</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-18 08:30</t>
+          <t>更新时间: 2026-08-18 10:09</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-18 10:09</t>
+          <t>更新时间: 2026-08-19 10:11</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-19 10:11</t>
+          <t>更新时间: 2026-08-20 10:11</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-20 10:11</t>
+          <t>更新时间: 2026-08-21 10:18</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-21 10:18</t>
+          <t>更新时间: 2026-08-22 10:08</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-22 10:08</t>
+          <t>更新时间: 2026-08-23 10:18</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-23 10:18</t>
+          <t>更新时间: 2026-08-24 10:16</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-24 10:16</t>
+          <t>更新时间: 2026-08-25 10:12</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-25 10:12</t>
+          <t>更新时间: 2026-08-26 10:18</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-26 10:18</t>
+          <t>更新时间: 2026-08-27 18:45</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-27 18:45</t>
+          <t>更新时间: 2026-08-28 20:22</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-28 20:22</t>
+          <t>更新时间: 2026-08-29 15:31</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-29 15:31</t>
+          <t>更新时间: 2026-08-30 14:04</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-30 14:04</t>
+          <t>更新时间: 2026-08-31 14:23</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-08-31 14:23</t>
+          <t>更新时间: 2026-09-01 13:52</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-01 13:52</t>
+          <t>更新时间: 2026-09-02 13:15</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-02 13:15</t>
+          <t>更新时间: 2026-09-03 13:20</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-03 13:20</t>
+          <t>更新时间: 2026-09-04 13:14</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-04 13:14</t>
+          <t>更新时间: 2026-09-05 13:03</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-05 13:03</t>
+          <t>更新时间: 2026-09-06 13:17</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-06 13:17</t>
+          <t>更新时间: 2026-09-07 13:26</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-07 13:26</t>
+          <t>更新时间: 2026-09-08 13:27</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-08 13:27</t>
+          <t>更新时间: 2026-09-09 13:32</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-09 13:32</t>
+          <t>更新时间: 2026-09-10 13:26</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-10 13:26</t>
+          <t>更新时间: 2026-09-11 13:24</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-11 13:24</t>
+          <t>更新时间: 2026-09-12 13:15</t>
         </is>
       </c>
     </row>
